--- a/Provodnik/_шаблоны/ВСОП_1.xlsx
+++ b/Provodnik/_шаблоны/ВСОП_1.xlsx
@@ -497,8 +497,8 @@
     <col min="2" max="2" width="36.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="16" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.28515625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="16" style="3" customWidth="1"/>
+    <col min="5" max="5" width="39.28515625" style="14" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="3" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="11.5703125" style="3" customWidth="1"/>
